--- a/workhourreport.xlsx
+++ b/workhourreport.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamdu\JAVA\final_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamdu\JAVA\organization-management-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B1F090-A80B-41FC-BAD0-DC03D44F44F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CECB93-5931-4E8E-A1CC-0F0E602D3CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{D598B82B-84B0-4546-BEE5-88F9719D2241}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Work-hour Report</t>
   </si>
@@ -52,12 +52,27 @@
   <si>
     <t>Finished requirements for 1 point.</t>
   </si>
+  <si>
+    <t>Finished requirements for 2 points.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,18 +98,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -427,23 +445,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58D7AD93-C613-49CE-9633-D69EC2D65C38}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.90625" customWidth="1"/>
-    <col min="2" max="2" width="16.08984375" customWidth="1"/>
-    <col min="3" max="3" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" customWidth="1"/>
+    <col min="3" max="3" width="31.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -454,12 +471,26 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
         <v>46132</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.5</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
